--- a/VerveStacks_VEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_VEN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VEN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59362C62-A6FF-43F6-9298-192D67A1A8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BBE19D-3DA7-4D7A-85CD-A3CC8FEDD4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2484" uniqueCount="748">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -2370,6 +2370,9 @@
   <si>
     <t>Transformer: e_w791120846-230 → e_w791120846-400</t>
   </si>
+  <si>
+    <t>e_VE1-230,e_VE10-230,e_VE11-230,e_VE12-230,e_VE13-230,e_VE2-230,e_VE24-230,e_VE25-230,e_VE3-230,e_VE4-230,e_VE4-400,e_VE5-230,e_VE5-400,e_VE52-230,e_VE58-230,e_VE59-230,e_VE6-230,e_VE8-230,e_VE9-230,e_w187936908-230,e_w187936908-400,e_w264134612-230,e_w264134612-400,e_w264156840-230,e_w264156841-230,e_w264156842-230,e_w265064743-400,e_w365007880-230,e_w365007880-400,e_w502761909-230,e_w565534382-230,e_w609494059-230,e_w677150278-230,e_w794639093-230,e_w798451066-230,e_w801987822-230</t>
+  </si>
 </sst>
 </file>
 
@@ -2383,7 +2386,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2531,15 +2534,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2631,11 +2627,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -2850,7 +2841,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2870,9 +2861,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -3264,7 +3254,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3284,9 +3273,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="20">
+  <cellStyles count="19">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
-    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -4262,7 +4250,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_VE1-230,e_VE10-230,e_VE11-230,e_VE12-230,e_VE13-230,e_VE2-230,e_VE24-230,e_VE25-230,e_VE3-230,e_VE4-230,e_VE4-400,e_VE5-230,e_VE5-400,e_VE52-230,e_VE58-230,e_VE59-230,e_VE6-230,e_VE8-230,e_VE9-230,e_w187936908-230,e_w187936908-400,e_w264134612-230,e_w264134612-400,e_w264156840-230,e_w264156841-230,e_w264156842-230,e_w265064743-400,e_w365007880-230,e_w365007880-400,e_w502761909-230,e_w565534382-230,e_w609494059-230,e_w677150278-230,e_w794639093-230,e_w798451066-230,e_w801987822-230</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -4284,7 +4272,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_VE1-230,e_VE10-230,e_VE11-230,e_VE12-230,e_VE13-230,e_VE2-230,e_VE24-230,e_VE25-230,e_VE3-230,e_VE4-230,e_VE4-400,e_VE5-230,e_VE5-400,e_VE52-230,e_VE58-230,e_VE59-230,e_VE6-230,e_VE8-230,e_VE9-230,e_w187936908-230,e_w187936908-400,e_w264134612-230,e_w264134612-400,e_w264156840-230,e_w264156841-230,e_w264156842-230,e_w265064743-400,e_w365007880-230,e_w365007880-400,e_w502761909-230,e_w565534382-230,e_w609494059-230,e_w677150278-230,e_w794639093-230,e_w798451066-230,e_w801987822-230</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -4298,8 +4286,8 @@
       <c r="S28">
         <v>50</v>
       </c>
-      <c r="V28" s="147" t="s">
-        <v>19</v>
+      <c r="V28" t="s">
+        <v>747</v>
       </c>
     </row>
   </sheetData>
@@ -5845,25 +5833,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="147" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149" t="s">
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="148"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="148" t="s">
+      <c r="G1" s="147"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="147" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="151" t="s">
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="150" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -5909,7 +5897,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="152"/>
+      <c r="O2" s="151"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5954,7 +5942,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="152"/>
+      <c r="O3" s="151"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5996,7 +5984,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="153"/>
+      <c r="O4" s="152"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
